--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>745.76</v>
+        <v>744.78</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>725.17</v>
+        <v>712.6044000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>299.32</v>
+        <v>297.58</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66.48</v>
+        <v>65.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>87.77</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.08</v>
+        <v>97.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>369.27</v>
+        <v>368.76</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>685.46</v>
+        <v>684.84</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>156.12</v>
+        <v>156.15</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>125.23</v>
+        <v>125.74</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>211</v>
+        <v>212.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>318.6</v>
+        <v>320.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>295.25</v>
+        <v>297</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.845</v>
+        <v>13.965</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.64</v>
+        <v>20.735</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5576</v>
+        <v>5595.25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>47.383</v>
+        <v>48.38</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89.928</v>
+        <v>90.316</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.44</v>
+        <v>22.74</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.549</v>
+        <v>3.55</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>744.78</v>
+        <v>751.28</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1122.979</v>
+        <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>20.32359</v>
+        <v>21.04929</v>
       </c>
       <c r="I2" t="n">
-        <v>12.94135</v>
+        <v>13.17906</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>712.6044000000001</v>
+        <v>722.8200000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2035.716</v>
+        <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>25.10232</v>
+        <v>26.01941</v>
       </c>
       <c r="I3" t="n">
-        <v>15.40778</v>
+        <v>15.63715</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>297.58</v>
+        <v>298.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1810.537</v>
+        <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>18.004021</v>
+        <v>19.21864</v>
       </c>
       <c r="I4" t="n">
-        <v>6.6865</v>
+        <v>7.094010000000001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>65.7</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2515.766</v>
+        <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>20.83724</v>
+        <v>23.059312</v>
       </c>
       <c r="I5" t="n">
-        <v>6.1811298</v>
+        <v>7.157040400000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>89.34999999999999</v>
+        <v>89.97</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>726.711</v>
+        <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>16.89808</v>
+        <v>18.38627</v>
       </c>
       <c r="I6" t="n">
-        <v>9.228989499999999</v>
+        <v>9.519318999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97.3</v>
+        <v>98.31</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -820,13 +820,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>987.5120000000001</v>
+        <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>16.78562</v>
+        <v>18.30828</v>
       </c>
       <c r="I7" t="n">
-        <v>8.765359999999999</v>
+        <v>9.132479999999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>368.76</v>
+        <v>371.67</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1144.105</v>
+        <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>20.190611</v>
+        <v>20.98792</v>
       </c>
       <c r="I8" t="n">
-        <v>11.9215295</v>
+        <v>12.14645</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>684.84</v>
+        <v>690.62</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1125.203</v>
+        <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>20.406839</v>
+        <v>21.16476</v>
       </c>
       <c r="I9" t="n">
-        <v>13.00996</v>
+        <v>13.24271</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>156.15</v>
+        <v>157.97</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1214.011</v>
+        <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>19.492501</v>
+        <v>20.64893</v>
       </c>
       <c r="I10" t="n">
-        <v>10.79104</v>
+        <v>11.1419</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>125.74</v>
+        <v>126.35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>212.7</v>
+        <v>212.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>208.845</v>
       </c>
       <c r="H13" t="n">
-        <v>16.425289</v>
+        <v>17.84753</v>
       </c>
       <c r="I13" t="n">
-        <v>9.87218</v>
+        <v>10.082111</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>320.7</v>
+        <v>319.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>297</v>
+        <v>298.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.965</v>
+        <v>13.95</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>968.739</v>
       </c>
       <c r="H17" t="n">
-        <v>13.28729</v>
+        <v>13.84245</v>
       </c>
       <c r="I17" t="n">
-        <v>10.219929</v>
+        <v>10.24766</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.735</v>
+        <v>20.69</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1226.953</v>
       </c>
       <c r="H18" t="n">
-        <v>16.17235</v>
+        <v>16.65703</v>
       </c>
       <c r="I18" t="n">
-        <v>10.910401</v>
+        <v>11.0153906</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5595.25</v>
+        <v>5616.75</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>48.38</v>
+        <v>48.493</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90.316</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.74</v>
+        <v>22.78</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.55</v>
+        <v>3.482</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>751.28</v>
+        <v>747.71</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>21.04929</v>
+        <v>20.95912</v>
       </c>
       <c r="I2" t="n">
-        <v>13.17906</v>
+        <v>12.99154</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>722.8200000000001</v>
+        <v>709.4299999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>26.01941</v>
+        <v>25.37531</v>
       </c>
       <c r="I3" t="n">
-        <v>15.63715</v>
+        <v>15.156959</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>298.9</v>
+        <v>296.19</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>19.21864</v>
+        <v>18.44182</v>
       </c>
       <c r="I4" t="n">
-        <v>7.094010000000001</v>
+        <v>7.09901</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>67.56999999999999</v>
+        <v>65.72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>23.059312</v>
+        <v>21.47014</v>
       </c>
       <c r="I5" t="n">
-        <v>7.157040400000001</v>
+        <v>6.587510000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>89.97</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>18.38627</v>
+        <v>17.720899</v>
       </c>
       <c r="I6" t="n">
-        <v>9.519318999999999</v>
+        <v>9.1562994</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>98.31</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>18.30828</v>
+        <v>17.433679</v>
       </c>
       <c r="I7" t="n">
-        <v>9.132479999999999</v>
+        <v>8.732199999999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>371.67</v>
+        <v>369.61</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>20.98792</v>
+        <v>20.8138</v>
       </c>
       <c r="I8" t="n">
-        <v>12.14645</v>
+        <v>11.99198</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>690.62</v>
+        <v>687.08</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>21.16476</v>
+        <v>21.05138</v>
       </c>
       <c r="I9" t="n">
-        <v>13.24271</v>
+        <v>13.048661</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>157.97</v>
+        <v>156.46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>20.64893</v>
+        <v>20.1828</v>
       </c>
       <c r="I10" t="n">
-        <v>11.1419</v>
+        <v>10.88065</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>126.35</v>
+        <v>125.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>212.8</v>
+        <v>210</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>208.845</v>
       </c>
       <c r="H13" t="n">
-        <v>17.84753</v>
+        <v>17.112601</v>
       </c>
       <c r="I13" t="n">
-        <v>10.082111</v>
+        <v>9.532499999999999</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>319.7</v>
+        <v>317.75</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>298.9</v>
+        <v>291.45</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2107.888</v>
       </c>
       <c r="H15" t="n">
-        <v>23.639311</v>
+        <v>23.24193</v>
       </c>
       <c r="I15" t="n">
-        <v>16.55345</v>
+        <v>15.83405</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.95</v>
+        <v>13.74</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>968.739</v>
       </c>
       <c r="H17" t="n">
-        <v>13.84245</v>
+        <v>13.30827</v>
       </c>
       <c r="I17" t="n">
-        <v>10.24766</v>
+        <v>9.766731</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.69</v>
+        <v>20.415</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1226.953</v>
       </c>
       <c r="H18" t="n">
-        <v>16.65703</v>
+        <v>15.923311</v>
       </c>
       <c r="I18" t="n">
-        <v>11.0153906</v>
+        <v>10.619701</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5616.75</v>
+        <v>5573</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>48.493</v>
+        <v>46.813</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90.73999999999999</v>
+        <v>90.05</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.78</v>
+        <v>22.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.482</v>
+        <v>3.54</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>747.71</v>
+        <v>745.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>20.95912</v>
+        <v>20.834431</v>
       </c>
       <c r="I2" t="n">
-        <v>12.99154</v>
+        <v>13.106559</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>709.4299999999999</v>
+        <v>711.4400000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>25.37531</v>
+        <v>25.4936</v>
       </c>
       <c r="I3" t="n">
-        <v>15.156959</v>
+        <v>15.36182</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>296.19</v>
+        <v>293.48</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>18.44182</v>
+        <v>18.079491</v>
       </c>
       <c r="I4" t="n">
-        <v>7.09901</v>
+        <v>7.1002305</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>65.72</v>
+        <v>66.23</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>21.47014</v>
+        <v>21.783541</v>
       </c>
       <c r="I5" t="n">
-        <v>6.587510000000001</v>
+        <v>7.20288</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>89.04000000000001</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>17.720899</v>
+        <v>17.340669</v>
       </c>
       <c r="I6" t="n">
-        <v>9.1562994</v>
+        <v>9.22622</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97.01000000000001</v>
+        <v>96.31</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>17.433679</v>
+        <v>17.150539</v>
       </c>
       <c r="I7" t="n">
-        <v>8.732199999999999</v>
+        <v>8.8685796</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>369.61</v>
+        <v>368.25</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>20.8138</v>
+        <v>20.66544</v>
       </c>
       <c r="I8" t="n">
-        <v>11.99198</v>
+        <v>12.0993406</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>687.08</v>
+        <v>685.26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>21.05138</v>
+        <v>20.9444</v>
       </c>
       <c r="I9" t="n">
-        <v>13.048661</v>
+        <v>13.169509</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>156.46</v>
+        <v>155.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>20.1828</v>
+        <v>20.03925</v>
       </c>
       <c r="I10" t="n">
-        <v>10.88065</v>
+        <v>11.04643</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>125.4</v>
+        <v>124.47</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>210</v>
+        <v>205.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>208.845</v>
       </c>
       <c r="H13" t="n">
-        <v>17.112601</v>
+        <v>16.2323</v>
       </c>
       <c r="I13" t="n">
-        <v>9.532499999999999</v>
+        <v>9.435</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>317.75</v>
+        <v>312.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>291.45</v>
+        <v>290.25</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2107.888</v>
       </c>
       <c r="H15" t="n">
-        <v>23.24193</v>
+        <v>23.07255</v>
       </c>
       <c r="I15" t="n">
-        <v>15.83405</v>
+        <v>16.01878</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.74</v>
+        <v>13.64</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>968.739</v>
       </c>
       <c r="H17" t="n">
-        <v>13.30827</v>
+        <v>13.03271</v>
       </c>
       <c r="I17" t="n">
-        <v>9.766731</v>
+        <v>9.927069400000001</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.415</v>
+        <v>20.185</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1226.953</v>
       </c>
       <c r="H18" t="n">
-        <v>15.923311</v>
+        <v>15.48633</v>
       </c>
       <c r="I18" t="n">
-        <v>10.619701</v>
+        <v>10.59457</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5573</v>
+        <v>5541.25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46.813</v>
+        <v>46.773</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90.05</v>
+        <v>89.36199999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.8</v>
+        <v>21.97</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>745.4</v>
+        <v>751.71</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>20.834431</v>
+        <v>21.17444</v>
       </c>
       <c r="I2" t="n">
-        <v>13.106559</v>
+        <v>13.05706</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>711.4400000000001</v>
+        <v>723.2258</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>25.4936</v>
+        <v>26.18594</v>
       </c>
       <c r="I3" t="n">
-        <v>15.36182</v>
+        <v>15.59928</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>293.48</v>
+        <v>297.24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>18.079491</v>
+        <v>18.58162</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1002305</v>
+        <v>6.9256</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66.23</v>
+        <v>66.78</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>21.783541</v>
+        <v>22.11972</v>
       </c>
       <c r="I5" t="n">
-        <v>7.20288</v>
+        <v>7.012880000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.18000000000001</v>
+        <v>88.41</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>17.340669</v>
+        <v>17.4426</v>
       </c>
       <c r="I6" t="n">
-        <v>9.22622</v>
+        <v>8.9404404</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.31</v>
+        <v>96.73</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>17.150539</v>
+        <v>17.32059</v>
       </c>
       <c r="I7" t="n">
-        <v>8.8685796</v>
+        <v>8.57432</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>368.25</v>
+        <v>371.45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>20.66544</v>
+        <v>21.01395</v>
       </c>
       <c r="I8" t="n">
-        <v>12.0993406</v>
+        <v>12.0237395</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>685.26</v>
+        <v>690.6900000000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>20.9444</v>
+        <v>21.26302</v>
       </c>
       <c r="I9" t="n">
-        <v>13.169509</v>
+        <v>13.11062</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>155.9</v>
+        <v>157.02</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>20.03925</v>
+        <v>20.32602</v>
       </c>
       <c r="I10" t="n">
-        <v>11.04643</v>
+        <v>10.91422</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>124.47</v>
+        <v>125.72</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>205.3</v>
+        <v>206.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1184,13 +1184,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>208.845</v>
+        <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>16.2323</v>
+        <v>16.53347</v>
       </c>
       <c r="I13" t="n">
-        <v>9.435</v>
+        <v>9.217040000000001</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>312.5</v>
+        <v>315.25</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>772.667</v>
+        <v>1058.402</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>290.25</v>
+        <v>297.15</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1306,13 +1306,13 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2107.888</v>
+        <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>23.07255</v>
+        <v>24.04018</v>
       </c>
       <c r="I15" t="n">
-        <v>16.01878</v>
+        <v>16.34696</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.64</v>
+        <v>13.835</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1428,13 +1428,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>968.739</v>
+        <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>13.03271</v>
+        <v>13.568811</v>
       </c>
       <c r="I17" t="n">
-        <v>9.927069400000001</v>
+        <v>9.988341</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.185</v>
+        <v>20.575</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1487,13 +1487,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1226.953</v>
+        <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>15.48633</v>
+        <v>16.225371</v>
       </c>
       <c r="I18" t="n">
-        <v>10.59457</v>
+        <v>10.75663</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5541.25</v>
+        <v>5591.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46.773</v>
+        <v>47.763</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89.36199999999999</v>
+        <v>90.246</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>21.97</v>
+        <v>22.14</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.51</v>
+        <v>3.476</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>751.71</v>
+        <v>754.95</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>723.2258</v>
+        <v>725.51</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>297.24</v>
+        <v>295.99</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66.78</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.41</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>17.4426</v>
+        <v>17.27943</v>
       </c>
       <c r="I6" t="n">
-        <v>8.9404404</v>
+        <v>8.9798495</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.73</v>
+        <v>97.22</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>371.45</v>
+        <v>372.69</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>21.01395</v>
+        <v>20.973021</v>
       </c>
       <c r="I8" t="n">
-        <v>12.0237395</v>
+        <v>12.098429</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>690.6900000000001</v>
+        <v>693.86</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>21.26302</v>
+        <v>21.33992</v>
       </c>
       <c r="I9" t="n">
-        <v>13.11062</v>
+        <v>13.21426</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>157.02</v>
+        <v>157.68</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>125.72</v>
+        <v>126.15</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>206.9</v>
+        <v>206.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>297.15</v>
+        <v>298.15</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>24.04018</v>
+        <v>24.505211</v>
       </c>
       <c r="I15" t="n">
-        <v>16.34696</v>
+        <v>16.425171</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.835</v>
+        <v>13.905</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.575</v>
+        <v>20.67</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5591.5</v>
+        <v>5606.25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>47.763</v>
+        <v>47.817</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90.246</v>
+        <v>90.54600000000001</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.14</v>
+        <v>22.48</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.476</v>
+        <v>3.526</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>754.95</v>
+        <v>749.17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>21.17444</v>
+        <v>20.041531</v>
       </c>
       <c r="I2" t="n">
-        <v>13.05706</v>
+        <v>12.97692</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>725.51</v>
+        <v>711.74</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>26.18594</v>
+        <v>24.07021</v>
       </c>
       <c r="I3" t="n">
-        <v>15.59928</v>
+        <v>15.13823</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>295.99</v>
+        <v>293.48</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>18.58162</v>
+        <v>16.27976</v>
       </c>
       <c r="I4" t="n">
-        <v>6.9256</v>
+        <v>7.0423596</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>22.11972</v>
+        <v>18.88106</v>
       </c>
       <c r="I5" t="n">
-        <v>7.012880000000001</v>
+        <v>6.2323198</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.56999999999999</v>
+        <v>87.86</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>17.27943</v>
+        <v>15.041761</v>
       </c>
       <c r="I6" t="n">
-        <v>8.9798495</v>
+        <v>8.83658</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97.22</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>17.32059</v>
+        <v>15.27506</v>
       </c>
       <c r="I7" t="n">
-        <v>8.57432</v>
+        <v>8.472519999999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>372.69</v>
+        <v>369.78</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>20.973021</v>
+        <v>19.701152</v>
       </c>
       <c r="I8" t="n">
-        <v>12.098429</v>
+        <v>11.98537</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>693.86</v>
+        <v>688.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>21.33992</v>
+        <v>20.128411</v>
       </c>
       <c r="I9" t="n">
-        <v>13.21426</v>
+        <v>13.03372</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>157.68</v>
+        <v>155.94</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>20.32602</v>
+        <v>18.71097</v>
       </c>
       <c r="I10" t="n">
-        <v>10.91422</v>
+        <v>10.772081</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>126.15</v>
+        <v>126.33</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>206.6</v>
+        <v>206.95</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>16.53347</v>
+        <v>15.22994</v>
       </c>
       <c r="I13" t="n">
-        <v>9.217040000000001</v>
+        <v>9.081759999999999</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>315.25</v>
+        <v>315.35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>298.15</v>
+        <v>296.45</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>24.505211</v>
+        <v>23.852609</v>
       </c>
       <c r="I15" t="n">
-        <v>16.425171</v>
+        <v>15.898961</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>13.568811</v>
+        <v>13.56497</v>
       </c>
       <c r="I17" t="n">
-        <v>9.988341</v>
+        <v>9.83868</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.67</v>
+        <v>20.59</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>16.225371</v>
+        <v>15.50922</v>
       </c>
       <c r="I18" t="n">
-        <v>10.75663</v>
+        <v>10.59418</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5606.25</v>
+        <v>5619.75</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>47.817</v>
+        <v>46.781</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90.54600000000001</v>
+        <v>90.672</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.48</v>
+        <v>22.39</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.526</v>
+        <v>3.616</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>749.17</v>
+        <v>751.83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>20.041531</v>
+        <v>20.208389</v>
       </c>
       <c r="I2" t="n">
-        <v>12.97692</v>
+        <v>13.02333</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>711.74</v>
+        <v>719.71</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>24.07021</v>
+        <v>24.53921</v>
       </c>
       <c r="I3" t="n">
-        <v>15.13823</v>
+        <v>15.35295</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>293.48</v>
+        <v>294.51</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>16.27976</v>
+        <v>16.79731</v>
       </c>
       <c r="I4" t="n">
-        <v>7.0423596</v>
+        <v>7.451039600000001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64.5</v>
+        <v>65.67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>18.88106</v>
+        <v>19.818741</v>
       </c>
       <c r="I5" t="n">
-        <v>6.2323198</v>
+        <v>6.523779999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>87.86</v>
+        <v>88.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>15.041761</v>
+        <v>15.41562</v>
       </c>
       <c r="I6" t="n">
-        <v>8.83658</v>
+        <v>8.910120000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.15000000000001</v>
+        <v>96.89</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>15.27506</v>
+        <v>15.79853</v>
       </c>
       <c r="I7" t="n">
-        <v>8.472519999999999</v>
+        <v>8.587250000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>369.78</v>
+        <v>371.16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>19.701152</v>
+        <v>19.90872</v>
       </c>
       <c r="I8" t="n">
-        <v>11.98537</v>
+        <v>12.0997</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>688.5</v>
+        <v>691.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>20.128411</v>
+        <v>20.31148</v>
       </c>
       <c r="I9" t="n">
-        <v>13.03372</v>
+        <v>13.08791</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>155.94</v>
+        <v>156.94</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>18.71097</v>
+        <v>19.0737</v>
       </c>
       <c r="I10" t="n">
-        <v>10.772081</v>
+        <v>10.88337</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>126.33</v>
+        <v>126.09</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>206.95</v>
+        <v>207.15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>15.22994</v>
+        <v>15.35809</v>
       </c>
       <c r="I13" t="n">
-        <v>9.081759999999999</v>
+        <v>9.109349999999999</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>315.35</v>
+        <v>315.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>296.45</v>
+        <v>297.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>23.852609</v>
+        <v>23.567529</v>
       </c>
       <c r="I15" t="n">
-        <v>15.898961</v>
+        <v>16.07899</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.905</v>
+        <v>13.8925</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>13.56497</v>
+        <v>13.54589</v>
       </c>
       <c r="I17" t="n">
-        <v>9.83868</v>
+        <v>9.92022</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.59</v>
+        <v>20.625</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>15.50922</v>
+        <v>15.44516</v>
       </c>
       <c r="I18" t="n">
-        <v>10.59418</v>
+        <v>10.78799</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5619.75</v>
+        <v>5609.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46.781</v>
+        <v>46.904</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90.672</v>
+        <v>90.54600000000001</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.39</v>
+        <v>22.57</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.616</v>
+        <v>3.615</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>751.83</v>
+        <v>754.8099999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>20.208389</v>
+        <v>20.36701</v>
       </c>
       <c r="I2" t="n">
-        <v>13.02333</v>
+        <v>13.19021</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>719.71</v>
+        <v>717.74</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>24.53921</v>
+        <v>24.426621</v>
       </c>
       <c r="I3" t="n">
-        <v>15.35295</v>
+        <v>15.45301</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>294.51</v>
+        <v>295.77</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>16.79731</v>
+        <v>16.963631</v>
       </c>
       <c r="I4" t="n">
-        <v>7.451039600000001</v>
+        <v>7.6651</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>65.67</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>19.818741</v>
+        <v>19.75789</v>
       </c>
       <c r="I5" t="n">
-        <v>6.523779999999999</v>
+        <v>6.44</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.3</v>
+        <v>89.12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>15.41562</v>
+        <v>15.77178</v>
       </c>
       <c r="I6" t="n">
-        <v>8.910120000000001</v>
+        <v>9.3472995</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.89</v>
+        <v>97.54000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>15.79853</v>
+        <v>16.0569</v>
       </c>
       <c r="I7" t="n">
-        <v>8.587250000000001</v>
+        <v>8.9551695</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>371.16</v>
+        <v>372.42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>19.90872</v>
+        <v>20.044251</v>
       </c>
       <c r="I8" t="n">
-        <v>12.0997</v>
+        <v>12.25467</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>691.1</v>
+        <v>693.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>20.31148</v>
+        <v>20.46795</v>
       </c>
       <c r="I9" t="n">
-        <v>13.08791</v>
+        <v>13.24909</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>156.94</v>
+        <v>157.52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>19.0737</v>
+        <v>19.2202</v>
       </c>
       <c r="I10" t="n">
-        <v>10.88337</v>
+        <v>11.0588506</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>126.09</v>
+        <v>126.29</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>207.15</v>
+        <v>206.15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>15.35809</v>
+        <v>15.17217</v>
       </c>
       <c r="I13" t="n">
-        <v>9.109349999999999</v>
+        <v>9.216601000000001</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>315.55</v>
+        <v>316.15</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>297.2</v>
+        <v>294.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>23.567529</v>
+        <v>23.22008</v>
       </c>
       <c r="I15" t="n">
-        <v>16.07899</v>
+        <v>16.01166</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.8925</v>
+        <v>13.825</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>13.54589</v>
+        <v>13.36169</v>
       </c>
       <c r="I17" t="n">
-        <v>9.92022</v>
+        <v>9.8894596</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.625</v>
+        <v>20.475</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>15.44516</v>
+        <v>15.164609</v>
       </c>
       <c r="I18" t="n">
-        <v>10.78799</v>
+        <v>10.6398</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5609.5</v>
+        <v>5582.25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46.904</v>
+        <v>46.759</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90.54600000000001</v>
+        <v>90.682</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.57</v>
+        <v>22.21</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.615</v>
+        <v>3.585</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>754.8099999999999</v>
+        <v>750.72</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>20.36701</v>
+        <v>20.14921</v>
       </c>
       <c r="I2" t="n">
-        <v>13.19021</v>
+        <v>13.24549</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>717.74</v>
+        <v>705.9400000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>24.426621</v>
+        <v>23.740971</v>
       </c>
       <c r="I3" t="n">
-        <v>15.45301</v>
+        <v>15.25818</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>295.77</v>
+        <v>295.59</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>16.963631</v>
+        <v>16.9399</v>
       </c>
       <c r="I4" t="n">
-        <v>7.6651</v>
+        <v>7.919099999999999</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>65.56999999999999</v>
+        <v>64.19</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>19.75789</v>
+        <v>18.91177</v>
       </c>
       <c r="I5" t="n">
-        <v>6.44</v>
+        <v>6.15376</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>89.12</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>15.77178</v>
+        <v>15.62871</v>
       </c>
       <c r="I6" t="n">
-        <v>9.3472995</v>
+        <v>9.412891</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97.54000000000001</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>16.0569</v>
+        <v>15.74671</v>
       </c>
       <c r="I7" t="n">
-        <v>8.9551695</v>
+        <v>8.943730599999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>372.42</v>
+        <v>370.58</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>20.044251</v>
+        <v>19.84622</v>
       </c>
       <c r="I8" t="n">
-        <v>12.25467</v>
+        <v>12.32047</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>693.8</v>
+        <v>690.14</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>20.46795</v>
+        <v>20.255738</v>
       </c>
       <c r="I9" t="n">
-        <v>13.24909</v>
+        <v>13.30622</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>157.52</v>
+        <v>156.36</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>19.2202</v>
+        <v>18.92683</v>
       </c>
       <c r="I10" t="n">
-        <v>11.0588506</v>
+        <v>11.06342</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>126.29</v>
+        <v>126.26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>206.15</v>
+        <v>205.45</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>15.17217</v>
+        <v>15.04166</v>
       </c>
       <c r="I13" t="n">
-        <v>9.216601000000001</v>
+        <v>9.2678204</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>316.15</v>
+        <v>316.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>294.7</v>
+        <v>292.85</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>23.22008</v>
+        <v>22.9617</v>
       </c>
       <c r="I15" t="n">
-        <v>16.01166</v>
+        <v>16.00827</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.825</v>
+        <v>13.815</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>13.36169</v>
+        <v>13.33435</v>
       </c>
       <c r="I17" t="n">
-        <v>9.8894596</v>
+        <v>9.9437304</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.475</v>
+        <v>20.46</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>15.164609</v>
+        <v>15.13648</v>
       </c>
       <c r="I18" t="n">
-        <v>10.6398</v>
+        <v>10.6684305</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5582.25</v>
+        <v>5589.75</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46.759</v>
+        <v>46.23</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90.682</v>
+        <v>90.626</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.21</v>
+        <v>22.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.585</v>
+        <v>3.597</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>750.72</v>
+        <v>743.29</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>20.14921</v>
+        <v>19.61323</v>
       </c>
       <c r="I2" t="n">
-        <v>13.24549</v>
+        <v>13.020429</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>705.9400000000001</v>
+        <v>695.33</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>23.740971</v>
+        <v>22.73703</v>
       </c>
       <c r="I3" t="n">
-        <v>15.25818</v>
+        <v>14.90962</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>295.59</v>
+        <v>294.04</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>16.9399</v>
+        <v>16.32161</v>
       </c>
       <c r="I4" t="n">
-        <v>7.919099999999999</v>
+        <v>7.80568</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64.19</v>
+        <v>63.29</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>18.91177</v>
+        <v>18.30535</v>
       </c>
       <c r="I5" t="n">
-        <v>6.15376</v>
+        <v>5.8544103</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.79000000000001</v>
+        <v>88.59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>15.62871</v>
+        <v>15.59675</v>
       </c>
       <c r="I6" t="n">
-        <v>9.412891</v>
+        <v>9.36356</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.76000000000001</v>
+        <v>96.25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>15.74671</v>
+        <v>15.57651</v>
       </c>
       <c r="I7" t="n">
-        <v>8.943730599999999</v>
+        <v>8.82864</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>370.58</v>
+        <v>367.01</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>19.84622</v>
+        <v>19.309379</v>
       </c>
       <c r="I8" t="n">
-        <v>12.32047</v>
+        <v>12.10322</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>690.14</v>
+        <v>683.17</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>20.255738</v>
+        <v>19.710489</v>
       </c>
       <c r="I9" t="n">
-        <v>13.30622</v>
+        <v>13.07643</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>156.36</v>
+        <v>155</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>18.92683</v>
+        <v>18.48003</v>
       </c>
       <c r="I10" t="n">
-        <v>11.06342</v>
+        <v>10.86954</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>126.26</v>
+        <v>124.85</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>205.45</v>
+        <v>204.65</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>15.04166</v>
+        <v>14.95465</v>
       </c>
       <c r="I13" t="n">
-        <v>9.2678204</v>
+        <v>9.182589500000001</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>316.5</v>
+        <v>315.45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>292.85</v>
+        <v>285.95</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>22.9617</v>
+        <v>22.0503</v>
       </c>
       <c r="I15" t="n">
-        <v>16.00827</v>
+        <v>15.45638</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.815</v>
+        <v>13.6775</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>13.33435</v>
+        <v>12.94718</v>
       </c>
       <c r="I17" t="n">
-        <v>9.9437304</v>
+        <v>9.724010499999999</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.46</v>
+        <v>20.225</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>15.13648</v>
+        <v>14.622751</v>
       </c>
       <c r="I18" t="n">
-        <v>10.6684305</v>
+        <v>10.41303</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5589.75</v>
+        <v>5533.25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46.23</v>
+        <v>45.323</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90.626</v>
+        <v>89.666</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.6</v>
+        <v>22.07</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.597</v>
+        <v>3.618</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>743.29</v>
+        <v>742.09</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>19.61323</v>
+        <v>19.43062</v>
       </c>
       <c r="I2" t="n">
-        <v>13.020429</v>
+        <v>12.99859</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>695.33</v>
+        <v>696.0599999999999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>22.73703</v>
+        <v>23.41218</v>
       </c>
       <c r="I3" t="n">
-        <v>14.90962</v>
+        <v>14.85739</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>294.04</v>
+        <v>292.31</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>16.32161</v>
+        <v>15.794711</v>
       </c>
       <c r="I4" t="n">
-        <v>7.80568</v>
+        <v>7.34599</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63.29</v>
+        <v>63.56</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>18.30535</v>
+        <v>19.13468</v>
       </c>
       <c r="I5" t="n">
-        <v>5.8544103</v>
+        <v>6.23559</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.59</v>
+        <v>87.69</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>15.59675</v>
+        <v>15.131</v>
       </c>
       <c r="I6" t="n">
-        <v>9.36356</v>
+        <v>9.459910499999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.25</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>15.57651</v>
+        <v>15.25355</v>
       </c>
       <c r="I7" t="n">
-        <v>8.82864</v>
+        <v>8.91574</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>367.01</v>
+        <v>366.25</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>19.309379</v>
+        <v>19.09643</v>
       </c>
       <c r="I8" t="n">
-        <v>12.10322</v>
+        <v>11.99337</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>683.17</v>
+        <v>682.21</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>19.710489</v>
+        <v>19.52852</v>
       </c>
       <c r="I9" t="n">
-        <v>13.07643</v>
+        <v>13.06802</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>155</v>
+        <v>154.48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>18.48003</v>
+        <v>18.34336</v>
       </c>
       <c r="I10" t="n">
-        <v>10.86954</v>
+        <v>10.88966</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>124.85</v>
+        <v>125.26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>204.65</v>
+        <v>204.75</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>14.95465</v>
+        <v>14.66214</v>
       </c>
       <c r="I13" t="n">
-        <v>9.182589500000001</v>
+        <v>9.652660000000001</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>315.45</v>
+        <v>314.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>285.95</v>
+        <v>289.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>22.0503</v>
+        <v>22.2175</v>
       </c>
       <c r="I15" t="n">
-        <v>15.45638</v>
+        <v>15.7516</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.6775</v>
+        <v>13.66</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>12.94718</v>
+        <v>12.539521</v>
       </c>
       <c r="I17" t="n">
-        <v>9.724010499999999</v>
+        <v>9.8239094</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.225</v>
+        <v>20.195</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>14.622751</v>
+        <v>14.2831</v>
       </c>
       <c r="I18" t="n">
-        <v>10.41303</v>
+        <v>10.5150804</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5533.25</v>
+        <v>5556.25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45.323</v>
+        <v>45.826</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89.666</v>
+        <v>89.94199999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.07</v>
+        <v>22.22</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.618</v>
+        <v>3.582</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>742.09</v>
+        <v>748.28</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>19.43062</v>
+        <v>19.761771</v>
       </c>
       <c r="I2" t="n">
-        <v>12.99859</v>
+        <v>13.00408</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>696.0599999999999</v>
+        <v>708.97</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>23.41218</v>
+        <v>24.294889</v>
       </c>
       <c r="I3" t="n">
-        <v>14.85739</v>
+        <v>15.10314</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>292.31</v>
+        <v>296.54</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>15.794711</v>
+        <v>16.47411</v>
       </c>
       <c r="I4" t="n">
-        <v>7.34599</v>
+        <v>7.28783</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63.56</v>
+        <v>65.34</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>19.13468</v>
+        <v>20.29619</v>
       </c>
       <c r="I5" t="n">
-        <v>6.23559</v>
+        <v>6.68716</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>87.69</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>15.131</v>
+        <v>15.46357</v>
       </c>
       <c r="I6" t="n">
-        <v>9.459910499999999</v>
+        <v>9.310839</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>95.56999999999999</v>
+        <v>96.92</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>15.25355</v>
+        <v>15.74341</v>
       </c>
       <c r="I7" t="n">
-        <v>8.91574</v>
+        <v>8.880330000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>366.25</v>
+        <v>369.45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>19.09643</v>
+        <v>19.44581</v>
       </c>
       <c r="I8" t="n">
-        <v>11.99337</v>
+        <v>11.9882494</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>682.21</v>
+        <v>687.87</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>19.52852</v>
+        <v>19.85336</v>
       </c>
       <c r="I9" t="n">
-        <v>13.06802</v>
+        <v>13.06559</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>154.48</v>
+        <v>156.29</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>18.34336</v>
+        <v>18.78356</v>
       </c>
       <c r="I10" t="n">
-        <v>10.88966</v>
+        <v>10.91541</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>125.26</v>
+        <v>125.75</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>204.75</v>
+        <v>206.25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1186,11 +1186,15 @@
       <c r="G13" t="n">
         <v>162.098</v>
       </c>
-      <c r="H13" t="n">
-        <v>14.66214</v>
-      </c>
-      <c r="I13" t="n">
-        <v>9.652660000000001</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1199,7 +1203,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>BlackRock Asset Management Deutschland AG - ETF</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1230,7 +1234,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>314.4</v>
+        <v>316.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1297,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>289.5</v>
+        <v>292.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1313,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>22.2175</v>
+        <v>22.94913</v>
       </c>
       <c r="I15" t="n">
-        <v>15.7516</v>
+        <v>15.887551</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1419,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.66</v>
+        <v>13.735</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1435,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>12.539521</v>
+        <v>12.6082</v>
       </c>
       <c r="I17" t="n">
-        <v>9.8239094</v>
+        <v>9.74601</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1478,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.195</v>
+        <v>20.29</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1494,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>14.2831</v>
+        <v>14.32839</v>
       </c>
       <c r="I18" t="n">
-        <v>10.5150804</v>
+        <v>10.43914</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1537,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5556.25</v>
+        <v>5585.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1665,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45.826</v>
+        <v>46.759</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1730,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89.94199999999999</v>
+        <v>90.288</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1858,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.22</v>
+        <v>22.57</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1921,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.582</v>
+        <v>3.553</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>748.28</v>
+        <v>747.41</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>19.761771</v>
+        <v>19.715339</v>
       </c>
       <c r="I2" t="n">
-        <v>13.00408</v>
+        <v>12.93053</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>708.97</v>
+        <v>705.35004</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>24.294889</v>
+        <v>24.08298</v>
       </c>
       <c r="I3" t="n">
-        <v>15.10314</v>
+        <v>14.833939</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>296.54</v>
+        <v>293.79</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>16.47411</v>
+        <v>16.112949</v>
       </c>
       <c r="I4" t="n">
-        <v>7.28783</v>
+        <v>7.43185</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>65.34</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>20.29619</v>
+        <v>20.08101</v>
       </c>
       <c r="I5" t="n">
-        <v>6.68716</v>
+        <v>6.5326</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.76000000000001</v>
+        <v>89.09</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>15.46357</v>
+        <v>15.60649</v>
       </c>
       <c r="I6" t="n">
-        <v>9.310839</v>
+        <v>9.356189500000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.92</v>
+        <v>97.09</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>15.74341</v>
+        <v>15.81104</v>
       </c>
       <c r="I7" t="n">
-        <v>8.880330000000001</v>
+        <v>8.898100000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>369.45</v>
+        <v>368.87</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>19.44581</v>
+        <v>19.38327</v>
       </c>
       <c r="I8" t="n">
-        <v>11.9882494</v>
+        <v>11.93417</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>687.87</v>
+        <v>687.03</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>19.85336</v>
+        <v>19.80455</v>
       </c>
       <c r="I9" t="n">
-        <v>13.06559</v>
+        <v>12.989931</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>156.29</v>
+        <v>156.19</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>18.78356</v>
+        <v>18.758209</v>
       </c>
       <c r="I10" t="n">
-        <v>10.91541</v>
+        <v>10.86413</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>125.75</v>
+        <v>126.03</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>206.25</v>
+        <v>207.35</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1186,15 +1186,11 @@
       <c r="G13" t="n">
         <v>162.098</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="H13" t="n">
+        <v>15.23602</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9.5024005</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1203,7 +1199,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BlackRock Asset Management Deutschland AG - ETF</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1234,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>316.3</v>
+        <v>318.05</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1297,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>292.5</v>
+        <v>292.65</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1313,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>22.94913</v>
+        <v>22.97014</v>
       </c>
       <c r="I15" t="n">
-        <v>15.887551</v>
+        <v>15.66565</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1419,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.735</v>
+        <v>13.76</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1435,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>12.6082</v>
+        <v>12.67648</v>
       </c>
       <c r="I17" t="n">
-        <v>9.74601</v>
+        <v>9.72242</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1478,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.29</v>
+        <v>20.315</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1494,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>14.32839</v>
+        <v>14.37532</v>
       </c>
       <c r="I18" t="n">
-        <v>10.43914</v>
+        <v>10.4932</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1537,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5585.5</v>
+        <v>5596.75</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1665,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46.759</v>
+        <v>46.645</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1730,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90.288</v>
+        <v>90.474</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1858,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.57</v>
+        <v>22.94</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1921,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.553</v>
+        <v>3.622</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>747.41</v>
+        <v>738.1799999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>19.715339</v>
+        <v>19.22049</v>
       </c>
       <c r="I2" t="n">
-        <v>12.93053</v>
+        <v>12.4198504</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>705.35004</v>
+        <v>691.96</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>24.08298</v>
+        <v>23.29278</v>
       </c>
       <c r="I3" t="n">
-        <v>14.833939</v>
+        <v>14.12929</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>293.79</v>
+        <v>292.09</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>16.112949</v>
+        <v>15.88855</v>
       </c>
       <c r="I4" t="n">
-        <v>7.43185</v>
+        <v>7.207339999999999</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64.98999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>20.08101</v>
+        <v>19.84033</v>
       </c>
       <c r="I5" t="n">
-        <v>6.5326</v>
+        <v>6.722690000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>89.09</v>
+        <v>87.83</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>15.60649</v>
+        <v>15.05889</v>
       </c>
       <c r="I6" t="n">
-        <v>9.356189500000001</v>
+        <v>8.85801</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>97.09</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>15.81104</v>
+        <v>15.27979</v>
       </c>
       <c r="I7" t="n">
-        <v>8.898100000000001</v>
+        <v>8.43901</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>368.87</v>
+        <v>364.69</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>19.38327</v>
+        <v>18.930611</v>
       </c>
       <c r="I8" t="n">
-        <v>11.93417</v>
+        <v>11.4575006</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>687.03</v>
+        <v>678.61</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>19.80455</v>
+        <v>19.31311</v>
       </c>
       <c r="I9" t="n">
-        <v>12.989931</v>
+        <v>12.487739</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>156.19</v>
+        <v>154.34</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>18.758209</v>
+        <v>18.28747</v>
       </c>
       <c r="I10" t="n">
-        <v>10.86413</v>
+        <v>10.46167</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>126.03</v>
+        <v>124.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>207.35</v>
+        <v>204.05</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>15.23602</v>
+        <v>14.62142</v>
       </c>
       <c r="I13" t="n">
-        <v>9.5024005</v>
+        <v>8.947230000000001</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>318.05</v>
+        <v>314.45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>292.65</v>
+        <v>285.65</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>22.97014</v>
+        <v>21.98176</v>
       </c>
       <c r="I15" t="n">
-        <v>15.66565</v>
+        <v>14.81923</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.76</v>
+        <v>13.5475</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>12.67648</v>
+        <v>12.093429</v>
       </c>
       <c r="I17" t="n">
-        <v>9.72242</v>
+        <v>9.174010000000001</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.315</v>
+        <v>20.01</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>14.37532</v>
+        <v>13.80004</v>
       </c>
       <c r="I18" t="n">
-        <v>10.4932</v>
+        <v>9.972810000000001</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5596.75</v>
+        <v>5533.75</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46.645</v>
+        <v>46.166</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90.474</v>
+        <v>89.352</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.94</v>
+        <v>22.29</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.622</v>
+        <v>3.593</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>738.1799999999999</v>
+        <v>738.9299999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>19.22049</v>
+        <v>19.0838</v>
       </c>
       <c r="I2" t="n">
-        <v>12.4198504</v>
+        <v>12.44269</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>691.96</v>
+        <v>684.23</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>23.29278</v>
+        <v>22.76662</v>
       </c>
       <c r="I3" t="n">
-        <v>14.12929</v>
+        <v>13.87315</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>292.09</v>
+        <v>291.17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>15.88855</v>
+        <v>15.67166</v>
       </c>
       <c r="I4" t="n">
-        <v>7.207339999999999</v>
+        <v>7.13972</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64.59999999999999</v>
+        <v>63.33</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>19.84033</v>
+        <v>18.51335</v>
       </c>
       <c r="I5" t="n">
-        <v>6.722690000000001</v>
+        <v>6.29973</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>87.83</v>
+        <v>88.41</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>15.05889</v>
+        <v>15.5062</v>
       </c>
       <c r="I6" t="n">
-        <v>8.85801</v>
+        <v>9.0014</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>95.76000000000001</v>
+        <v>96.34</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>15.27979</v>
+        <v>15.612529</v>
       </c>
       <c r="I7" t="n">
-        <v>8.43901</v>
+        <v>8.57006</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>364.69</v>
+        <v>364.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>18.930611</v>
+        <v>18.80225</v>
       </c>
       <c r="I8" t="n">
-        <v>11.4575006</v>
+        <v>11.464229</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>678.61</v>
+        <v>679.14</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>19.31311</v>
+        <v>19.176161</v>
       </c>
       <c r="I9" t="n">
-        <v>12.487739</v>
+        <v>12.505299</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>154.34</v>
+        <v>154.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>18.28747</v>
+        <v>18.13677</v>
       </c>
       <c r="I10" t="n">
-        <v>10.46167</v>
+        <v>10.45594</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>124.4</v>
+        <v>125.26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>204.05</v>
+        <v>206.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>14.62142</v>
+        <v>15.10731</v>
       </c>
       <c r="I13" t="n">
-        <v>8.947230000000001</v>
+        <v>9.249880000000001</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>314.45</v>
+        <v>317.15</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>285.65</v>
+        <v>285.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>21.98176</v>
+        <v>21.90218</v>
       </c>
       <c r="I15" t="n">
-        <v>14.81923</v>
+        <v>14.78303</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.5475</v>
+        <v>13.665</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>12.093429</v>
+        <v>12.27086</v>
       </c>
       <c r="I17" t="n">
-        <v>9.174010000000001</v>
+        <v>9.3627304</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.01</v>
+        <v>20.14</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>13.80004</v>
+        <v>13.99001</v>
       </c>
       <c r="I18" t="n">
-        <v>9.972810000000001</v>
+        <v>10.11534</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5533.75</v>
+        <v>5558</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46.166</v>
+        <v>45.926</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89.352</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.29</v>
+        <v>22.86</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.593</v>
+        <v>3.598</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>738.9299999999999</v>
+        <v>739.09</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>19.0838</v>
+        <v>19.24222</v>
       </c>
       <c r="I2" t="n">
-        <v>12.44269</v>
+        <v>12.49516</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>684.23</v>
+        <v>682.12</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>22.76662</v>
+        <v>22.59795</v>
       </c>
       <c r="I3" t="n">
-        <v>13.87315</v>
+        <v>14.03732</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>291.17</v>
+        <v>292.91</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>15.67166</v>
+        <v>16.104469</v>
       </c>
       <c r="I4" t="n">
-        <v>7.13972</v>
+        <v>7.4570596</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63.33</v>
+        <v>63.62</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>18.51335</v>
+        <v>18.626289</v>
       </c>
       <c r="I5" t="n">
-        <v>6.29973</v>
+        <v>7.24344</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.41</v>
+        <v>88.84</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>15.5062</v>
+        <v>15.77272</v>
       </c>
       <c r="I6" t="n">
-        <v>9.0014</v>
+        <v>9.071870000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.34</v>
+        <v>96.83</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>15.612529</v>
+        <v>15.70199</v>
       </c>
       <c r="I7" t="n">
-        <v>8.57006</v>
+        <v>8.7294</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>364.8</v>
+        <v>365.18</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>18.80225</v>
+        <v>19.0208</v>
       </c>
       <c r="I8" t="n">
-        <v>11.464229</v>
+        <v>11.56308</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>679.14</v>
+        <v>679.3099999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>19.176161</v>
+        <v>19.33019</v>
       </c>
       <c r="I9" t="n">
-        <v>12.505299</v>
+        <v>12.55383</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>154.3</v>
+        <v>154.61</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>18.13677</v>
+        <v>18.28403</v>
       </c>
       <c r="I10" t="n">
-        <v>10.45594</v>
+        <v>10.66286</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>125.26</v>
+        <v>124.75</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>206.9</v>
+        <v>209.15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>15.10731</v>
+        <v>15.01102</v>
       </c>
       <c r="I13" t="n">
-        <v>9.249880000000001</v>
+        <v>9.6952</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>317.15</v>
+        <v>317.25</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>285.2</v>
+        <v>280.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>21.90218</v>
+        <v>20.177759</v>
       </c>
       <c r="I15" t="n">
-        <v>14.78303</v>
+        <v>14.89603</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.665</v>
+        <v>13.5775</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>12.27086</v>
+        <v>11.55618</v>
       </c>
       <c r="I17" t="n">
-        <v>9.3627304</v>
+        <v>9.505850000000001</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.14</v>
+        <v>19.945</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>13.99001</v>
+        <v>13.509731</v>
       </c>
       <c r="I18" t="n">
-        <v>10.11534</v>
+        <v>10.01649</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5558</v>
+        <v>5536.25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45.926</v>
+        <v>45.34</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89.98999999999999</v>
+        <v>89.562</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.86</v>
+        <v>23.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.598</v>
+        <v>3.657</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>739.09</v>
+        <v>740.86</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>19.24222</v>
+        <v>18.95041</v>
       </c>
       <c r="I2" t="n">
-        <v>12.49516</v>
+        <v>12.55822</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>682.12</v>
+        <v>675.49</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>22.59795</v>
+        <v>21.4664</v>
       </c>
       <c r="I3" t="n">
-        <v>14.03732</v>
+        <v>13.72753</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>292.91</v>
+        <v>293.37</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>16.104469</v>
+        <v>15.66831</v>
       </c>
       <c r="I4" t="n">
-        <v>7.4570596</v>
+        <v>7.1774304</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iShares MSCI Emerging Markets ETF</t>
+          <t>iShares MSCI Emerging Index Fun</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63.62</v>
+        <v>62.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>18.626289</v>
+        <v>16.90311</v>
       </c>
       <c r="I5" t="n">
-        <v>7.24344</v>
+        <v>6.24461</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Europe ETF</t>
+          <t>Vanguard FTSEEuropean ETF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.84</v>
+        <v>89.23</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>15.77272</v>
+        <v>15.61235</v>
       </c>
       <c r="I6" t="n">
-        <v>9.071870000000001</v>
+        <v>9.05536</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.83</v>
+        <v>96.75</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>15.70199</v>
+        <v>15.414649</v>
       </c>
       <c r="I7" t="n">
-        <v>8.7294</v>
+        <v>8.61619</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vanguard Total Stock Market Index Fund ETF Shares</t>
+          <t>Vanguard Morningstar Total Stock Market ETF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>365.18</v>
+        <v>365.99</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>19.0208</v>
+        <v>18.697491</v>
       </c>
       <c r="I8" t="n">
-        <v>11.56308</v>
+        <v>11.57809</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>679.3099999999999</v>
+        <v>680.96</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>19.33019</v>
+        <v>19.0415</v>
       </c>
       <c r="I9" t="n">
-        <v>12.55383</v>
+        <v>12.62073</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>154.61</v>
+        <v>154.54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>18.28403</v>
+        <v>17.855431</v>
       </c>
       <c r="I10" t="n">
-        <v>10.66286</v>
+        <v>10.5508</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>124.75</v>
+        <v>125.18</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>209.15</v>
+        <v>210</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>15.01102</v>
+        <v>15.01067</v>
       </c>
       <c r="I13" t="n">
-        <v>9.6952</v>
+        <v>9.70767</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>317.25</v>
+        <v>318.35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>280.8</v>
+        <v>279.95</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>20.177759</v>
+        <v>20.15052</v>
       </c>
       <c r="I15" t="n">
-        <v>14.89603</v>
+        <v>14.49843</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.5775</v>
+        <v>13.64</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>11.55618</v>
+        <v>11.91815</v>
       </c>
       <c r="I17" t="n">
-        <v>9.505850000000001</v>
+        <v>9.45457</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19.945</v>
+        <v>20.115</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>13.509731</v>
+        <v>13.92189</v>
       </c>
       <c r="I18" t="n">
-        <v>10.01649</v>
+        <v>10.14116</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5536.25</v>
+        <v>5567.75</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45.34</v>
+        <v>44.952</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89.562</v>
+        <v>89.892</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>23.2</v>
+        <v>23.25</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.657</v>
+        <v>3.726</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>740.86</v>
+        <v>729.46</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>18.95041</v>
+        <v>18.33714</v>
       </c>
       <c r="I2" t="n">
-        <v>12.55822</v>
+        <v>12.11683</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>675.49</v>
+        <v>661.73</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>21.4664</v>
+        <v>20.63596</v>
       </c>
       <c r="I3" t="n">
-        <v>13.72753</v>
+        <v>13.22017</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>293.37</v>
+        <v>288.57</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>15.66831</v>
+        <v>15.034</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1774304</v>
+        <v>6.660670000000001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62.36</v>
+        <v>61.07</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>16.90311</v>
+        <v>16.09139</v>
       </c>
       <c r="I5" t="n">
-        <v>6.24461</v>
+        <v>5.69555</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>89.23</v>
+        <v>88.86</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>15.61235</v>
+        <v>15.45233</v>
       </c>
       <c r="I6" t="n">
-        <v>9.05536</v>
+        <v>8.79644</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.75</v>
+        <v>96.23</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>15.414649</v>
+        <v>15.20751</v>
       </c>
       <c r="I7" t="n">
-        <v>8.61619</v>
+        <v>8.350290000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>365.99</v>
+        <v>360.42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>18.697491</v>
+        <v>18.09226</v>
       </c>
       <c r="I8" t="n">
-        <v>11.57809</v>
+        <v>11.13865</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>680.96</v>
+        <v>670.63</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>19.0415</v>
+        <v>18.436489</v>
       </c>
       <c r="I9" t="n">
-        <v>12.62073</v>
+        <v>12.1803395</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>154.54</v>
+        <v>152.47</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>17.855431</v>
+        <v>17.326851</v>
       </c>
       <c r="I10" t="n">
-        <v>10.5508</v>
+        <v>10.13253</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>125.18</v>
+        <v>124.33</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>210</v>
+        <v>209.85</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>15.01067</v>
+        <v>14.98327</v>
       </c>
       <c r="I13" t="n">
-        <v>9.70767</v>
+        <v>9.60256</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>318.35</v>
+        <v>317.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>279.95</v>
+        <v>276.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>20.15052</v>
+        <v>19.61162</v>
       </c>
       <c r="I15" t="n">
-        <v>14.49843</v>
+        <v>14.28982</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.64</v>
+        <v>13.555</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>11.91815</v>
+        <v>11.68518</v>
       </c>
       <c r="I17" t="n">
-        <v>9.45457</v>
+        <v>9.23616</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.115</v>
+        <v>19.945</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>13.92189</v>
+        <v>13.600041</v>
       </c>
       <c r="I18" t="n">
-        <v>10.14116</v>
+        <v>9.751700599999999</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5567.75</v>
+        <v>5526.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>44.952</v>
+        <v>44.046</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89.892</v>
+        <v>89.286</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>23.25</v>
+        <v>22.82</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.726</v>
+        <v>3.665</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1944,8 +1944,10 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>0.291</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>729.46</v>
+        <v>741.6900000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>18.33714</v>
+        <v>18.99481</v>
       </c>
       <c r="I2" t="n">
-        <v>12.11683</v>
+        <v>12.59985</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>661.73</v>
+        <v>683.55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>20.63596</v>
+        <v>21.9476</v>
       </c>
       <c r="I3" t="n">
-        <v>13.22017</v>
+        <v>14.07633</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>288.57</v>
+        <v>292.59</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>15.034</v>
+        <v>15.5657</v>
       </c>
       <c r="I4" t="n">
-        <v>6.660670000000001</v>
+        <v>7.098069999999999</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61.07</v>
+        <v>63.59</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>16.09139</v>
+        <v>17.66672</v>
       </c>
       <c r="I5" t="n">
-        <v>5.69555</v>
+        <v>6.75949</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>88.86</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>15.45233</v>
+        <v>16.367531</v>
       </c>
       <c r="I6" t="n">
-        <v>8.79644</v>
+        <v>9.415010000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>96.23</v>
+        <v>98.88</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>15.20751</v>
+        <v>16.25548</v>
       </c>
       <c r="I7" t="n">
-        <v>8.350290000000001</v>
+        <v>9.067169999999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>360.42</v>
+        <v>366.27</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>18.09226</v>
+        <v>18.727751</v>
       </c>
       <c r="I8" t="n">
-        <v>11.13865</v>
+        <v>11.629599</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>670.63</v>
+        <v>681.79</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>18.436489</v>
+        <v>19.08985</v>
       </c>
       <c r="I9" t="n">
-        <v>12.1803395</v>
+        <v>12.66158</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>152.47</v>
+        <v>155.66</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>17.326851</v>
+        <v>18.13945</v>
       </c>
       <c r="I10" t="n">
-        <v>10.13253</v>
+        <v>10.7149094</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>124.33</v>
+        <v>123.69</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>209.85</v>
+        <v>211.15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>14.98327</v>
+        <v>15.220219</v>
       </c>
       <c r="I13" t="n">
-        <v>9.60256</v>
+        <v>9.86084</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>317.3</v>
+        <v>319.95</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>276.2</v>
+        <v>278.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>19.61162</v>
+        <v>19.885269</v>
       </c>
       <c r="I15" t="n">
-        <v>14.28982</v>
+        <v>14.61218</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.555</v>
+        <v>13.485</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>11.68518</v>
+        <v>11.4926</v>
       </c>
       <c r="I17" t="n">
-        <v>9.23616</v>
+        <v>9.19839</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19.945</v>
+        <v>19.935</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>13.600041</v>
+        <v>13.58105</v>
       </c>
       <c r="I18" t="n">
-        <v>9.751700599999999</v>
+        <v>9.828520000000001</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5526.5</v>
+        <v>5471.25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>44.046</v>
+        <v>44.737</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89.286</v>
+        <v>88.78</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.82</v>
+        <v>23.96</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.665</v>
+        <v>3.602</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1944,10 +1944,8 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="J25" t="n">
+        <v>0.291</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>741.6900000000001</v>
+        <v>747.03</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>18.99481</v>
+        <v>19.2041</v>
       </c>
       <c r="I2" t="n">
-        <v>12.59985</v>
+        <v>12.76153</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>683.55</v>
+        <v>687.99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>21.9476</v>
+        <v>22.18983</v>
       </c>
       <c r="I3" t="n">
-        <v>14.07633</v>
+        <v>14.22415</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>292.59</v>
+        <v>291.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>15.5657</v>
+        <v>14.93941</v>
       </c>
       <c r="I4" t="n">
-        <v>7.098069999999999</v>
+        <v>6.99612</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iShares MSCI Emerging Index Fun</t>
+          <t>iShares MSCI Emerging Markets ETF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63.59</v>
+        <v>64.09</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>17.66672</v>
+        <v>17.955561</v>
       </c>
       <c r="I5" t="n">
-        <v>6.75949</v>
+        <v>6.9268495</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vanguard FTSEEuropean ETF</t>
+          <t>Vanguard FTSE Europe ETF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>90.98999999999999</v>
+        <v>90.59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>16.367531</v>
+        <v>16.20896</v>
       </c>
       <c r="I6" t="n">
-        <v>9.415010000000001</v>
+        <v>9.31864</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>98.88</v>
+        <v>98.25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>16.25548</v>
+        <v>16.024731</v>
       </c>
       <c r="I7" t="n">
-        <v>9.067169999999999</v>
+        <v>8.92784</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>366.27</v>
+        <v>368.21</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>18.727751</v>
+        <v>18.81709</v>
       </c>
       <c r="I8" t="n">
-        <v>11.629599</v>
+        <v>11.7475994</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>681.79</v>
+        <v>686.65</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>19.08985</v>
+        <v>19.295481</v>
       </c>
       <c r="I9" t="n">
-        <v>12.66158</v>
+        <v>12.82174</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>155.66</v>
+        <v>156.43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>18.13945</v>
+        <v>18.25848</v>
       </c>
       <c r="I10" t="n">
-        <v>10.7149094</v>
+        <v>10.82423</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>123.69</v>
+        <v>124.23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>211.15</v>
+        <v>211.35</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>15.220219</v>
+        <v>15.28444</v>
       </c>
       <c r="I13" t="n">
-        <v>9.86084</v>
+        <v>9.88165</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>319.95</v>
+        <v>319.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>278.1</v>
+        <v>279.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>19.885269</v>
+        <v>20.10539</v>
       </c>
       <c r="I15" t="n">
-        <v>14.61218</v>
+        <v>14.73555</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.485</v>
+        <v>13.51</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>11.4926</v>
+        <v>11.5184896</v>
       </c>
       <c r="I17" t="n">
-        <v>9.19839</v>
+        <v>9.2388496</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19.935</v>
+        <v>20.09</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>13.58105</v>
+        <v>13.811961</v>
       </c>
       <c r="I18" t="n">
-        <v>9.828520000000001</v>
+        <v>9.998780500000001</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5471.25</v>
+        <v>5501</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>44.737</v>
+        <v>45.356</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>88.78</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>23.96</v>
+        <v>24.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.883</v>
+        <v>0.89</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.602</v>
+        <v>3.584</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.291</v>
+        <v>0.288</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>747.03</v>
+        <v>757.67</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>687.99</v>
+        <v>700.0700000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>291.2</v>
+        <v>296.22</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64.09</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>90.59</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>98.25</v>
+        <v>98.67</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>368.21</v>
+        <v>373.84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>686.65</v>
+        <v>696.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>156.43</v>
+        <v>157.94</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>124.23</v>
+        <v>126.12</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>211.35</v>
+        <v>214.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>15.28444</v>
+        <v>17.1944</v>
       </c>
       <c r="I13" t="n">
-        <v>9.88165</v>
+        <v>10.186949</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>319.4</v>
+        <v>320.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>279.6</v>
+        <v>285.35</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.51</v>
+        <v>13.64</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.09</v>
+        <v>20.315</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5501</v>
+        <v>5620.25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45.356</v>
+        <v>45.475</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>89.23999999999999</v>
+        <v>90.58799999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.2</v>
+        <v>24.68</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.584</v>
+        <v>3.664</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>757.67</v>
+        <v>771.33</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1016.428</v>
       </c>
       <c r="H2" t="n">
-        <v>19.2041</v>
+        <v>20.55821</v>
       </c>
       <c r="I2" t="n">
-        <v>12.76153</v>
+        <v>12.94526</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>700.0700000000001</v>
+        <v>723.85</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>2018.788</v>
       </c>
       <c r="H3" t="n">
-        <v>22.18983</v>
+        <v>23.97535</v>
       </c>
       <c r="I3" t="n">
-        <v>14.22415</v>
+        <v>14.482139</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>296.22</v>
+        <v>301.71</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>2248.413</v>
       </c>
       <c r="H4" t="n">
-        <v>14.93941</v>
+        <v>16.41225</v>
       </c>
       <c r="I4" t="n">
-        <v>6.99612</v>
+        <v>7.38097</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64.31999999999999</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>2574.804</v>
       </c>
       <c r="H5" t="n">
-        <v>17.955561</v>
+        <v>19.401011</v>
       </c>
       <c r="I5" t="n">
-        <v>6.9268495</v>
+        <v>6.76046</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>90.93000000000001</v>
+        <v>91.84</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>790.956</v>
       </c>
       <c r="H6" t="n">
-        <v>16.20896</v>
+        <v>17.608601</v>
       </c>
       <c r="I6" t="n">
-        <v>9.31864</v>
+        <v>9.140560000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>98.67</v>
+        <v>99.88</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>992.966</v>
       </c>
       <c r="H7" t="n">
-        <v>16.024731</v>
+        <v>17.47049</v>
       </c>
       <c r="I7" t="n">
-        <v>8.92784</v>
+        <v>8.757210000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>373.84</v>
+        <v>380.82</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1107.125</v>
       </c>
       <c r="H8" t="n">
-        <v>18.81709</v>
+        <v>20.214519</v>
       </c>
       <c r="I8" t="n">
-        <v>11.7475994</v>
+        <v>11.95914</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>696.4</v>
+        <v>708.98</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1018.984</v>
       </c>
       <c r="H9" t="n">
-        <v>19.295481</v>
+        <v>20.65431</v>
       </c>
       <c r="I9" t="n">
-        <v>12.82174</v>
+        <v>13.00444</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>157.94</v>
+        <v>160.63</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1164.005</v>
       </c>
       <c r="H10" t="n">
-        <v>18.25848</v>
+        <v>19.67009</v>
       </c>
       <c r="I10" t="n">
-        <v>10.82423</v>
+        <v>10.8684994</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>126.12</v>
+        <v>127.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>214.4</v>
+        <v>216.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>17.1944</v>
+        <v>17.38009</v>
       </c>
       <c r="I13" t="n">
-        <v>10.186949</v>
+        <v>10.18143</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>320.9</v>
+        <v>323.25</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>285.35</v>
+        <v>293.75</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>20.10539</v>
+        <v>21.6665</v>
       </c>
       <c r="I15" t="n">
-        <v>14.73555</v>
+        <v>15.20691</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.64</v>
+        <v>13.845</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>11.5184896</v>
+        <v>12.66118</v>
       </c>
       <c r="I17" t="n">
-        <v>9.2388496</v>
+        <v>9.338340000000001</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.315</v>
+        <v>20.685</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>13.811961</v>
+        <v>15.00701</v>
       </c>
       <c r="I18" t="n">
-        <v>9.998780500000001</v>
+        <v>10.173509</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5620.25</v>
+        <v>5704.25</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45.475</v>
+        <v>46.765</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90.58799999999999</v>
+        <v>91.72799999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.68</v>
+        <v>24.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.664</v>
+        <v>3.655</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>771.33</v>
+        <v>769.79</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1016.428</v>
+        <v>1008.633</v>
       </c>
       <c r="H2" t="n">
-        <v>20.55821</v>
+        <v>21.38091</v>
       </c>
       <c r="I2" t="n">
-        <v>12.94526</v>
+        <v>13.27301</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>723.85</v>
+        <v>717.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2018.788</v>
+        <v>1225.467</v>
       </c>
       <c r="H3" t="n">
-        <v>23.97535</v>
+        <v>25.17986</v>
       </c>
       <c r="I3" t="n">
-        <v>14.482139</v>
+        <v>14.86164</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>301.71</v>
+        <v>299.77</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2248.413</v>
+        <v>1877.073</v>
       </c>
       <c r="H4" t="n">
-        <v>16.41225</v>
+        <v>16.95365</v>
       </c>
       <c r="I4" t="n">
-        <v>7.38097</v>
+        <v>7.523440000000001</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>65.72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2574.804</v>
+        <v>1830.462</v>
       </c>
       <c r="H5" t="n">
-        <v>19.401011</v>
+        <v>20.31052</v>
       </c>
       <c r="I5" t="n">
-        <v>6.76046</v>
+        <v>7.14332</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>91.84</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>790.956</v>
+        <v>1045.822</v>
       </c>
       <c r="H6" t="n">
-        <v>17.608601</v>
+        <v>17.93362</v>
       </c>
       <c r="I6" t="n">
-        <v>9.140560000000001</v>
+        <v>9.266120000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>99.88</v>
+        <v>100.04</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -820,13 +820,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>992.966</v>
+        <v>1164.914</v>
       </c>
       <c r="H7" t="n">
-        <v>17.47049</v>
+        <v>17.88336</v>
       </c>
       <c r="I7" t="n">
-        <v>8.757210000000001</v>
+        <v>9.026209999999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>380.82</v>
+        <v>379.65</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1107.125</v>
+        <v>1050.409</v>
       </c>
       <c r="H8" t="n">
-        <v>20.214519</v>
+        <v>21.00551</v>
       </c>
       <c r="I8" t="n">
-        <v>11.95914</v>
+        <v>12.24598</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>708.98</v>
+        <v>707.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1018.984</v>
+        <v>1011.602</v>
       </c>
       <c r="H9" t="n">
-        <v>20.65431</v>
+        <v>21.49638</v>
       </c>
       <c r="I9" t="n">
-        <v>13.00444</v>
+        <v>13.33321</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>160.63</v>
+        <v>160.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1164.005</v>
+        <v>1123.254</v>
       </c>
       <c r="H10" t="n">
-        <v>19.67009</v>
+        <v>20.396139</v>
       </c>
       <c r="I10" t="n">
-        <v>10.8684994</v>
+        <v>11.1759394</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>127.8</v>
+        <v>128.26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>216.1</v>
+        <v>215.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>17.38009</v>
+        <v>17.25321</v>
       </c>
       <c r="I13" t="n">
-        <v>10.18143</v>
+        <v>10.02081</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>323.25</v>
+        <v>323.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>293.75</v>
+        <v>294.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>21.6665</v>
+        <v>23.08479</v>
       </c>
       <c r="I15" t="n">
-        <v>15.20691</v>
+        <v>15.550649</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.845</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>12.66118</v>
+        <v>13.39729</v>
       </c>
       <c r="I17" t="n">
-        <v>9.338340000000001</v>
+        <v>9.542619400000001</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.685</v>
+        <v>20.86</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>15.00701</v>
+        <v>15.82438</v>
       </c>
       <c r="I18" t="n">
-        <v>10.173509</v>
+        <v>10.74071</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5704.25</v>
+        <v>5729</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46.765</v>
+        <v>46.799</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>91.72799999999999</v>
+        <v>92.08199999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.6</v>
+        <v>24.29</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.655</v>
+        <v>3.614</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>

--- a/lista_completa_etfs_morningstar.xlsx
+++ b/lista_completa_etfs_morningstar.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>769.79</v>
+        <v>768.5599999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         <v>1008.633</v>
       </c>
       <c r="H2" t="n">
-        <v>21.38091</v>
+        <v>21.31623</v>
       </c>
       <c r="I2" t="n">
-        <v>13.27301</v>
+        <v>13.1994</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>717.3</v>
+        <v>714.65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         <v>1225.467</v>
       </c>
       <c r="H3" t="n">
-        <v>25.17986</v>
+        <v>25.02552</v>
       </c>
       <c r="I3" t="n">
-        <v>14.86164</v>
+        <v>14.87751</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>299.77</v>
+        <v>298.25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>1877.073</v>
       </c>
       <c r="H4" t="n">
-        <v>16.95365</v>
+        <v>16.75564</v>
       </c>
       <c r="I4" t="n">
-        <v>7.523440000000001</v>
+        <v>7.283069999999999</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iShares MSCI Emerging Markets ETF</t>
+          <t>iShares MSCI Emerging Index Fun</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>65.72</v>
+        <v>65.02</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         <v>1830.462</v>
       </c>
       <c r="H5" t="n">
-        <v>20.31052</v>
+        <v>19.88184</v>
       </c>
       <c r="I5" t="n">
-        <v>7.14332</v>
+        <v>7.09462</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vanguard FTSE Europe ETF</t>
+          <t>Vanguard FTSEEuropean ETF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>91.84999999999999</v>
+        <v>91.83</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>1045.822</v>
       </c>
       <c r="H6" t="n">
-        <v>17.93362</v>
+        <v>17.92506</v>
       </c>
       <c r="I6" t="n">
-        <v>9.266120000000001</v>
+        <v>9.381010400000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>100.04</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -823,10 +823,10 @@
         <v>1164.914</v>
       </c>
       <c r="H7" t="n">
-        <v>17.88336</v>
+        <v>17.86372</v>
       </c>
       <c r="I7" t="n">
-        <v>9.026209999999999</v>
+        <v>9.09807</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>379.65</v>
+        <v>379.07</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
         <v>1050.409</v>
       </c>
       <c r="H8" t="n">
-        <v>21.00551</v>
+        <v>20.943859</v>
       </c>
       <c r="I8" t="n">
-        <v>12.24598</v>
+        <v>12.18419</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>707.6</v>
+        <v>706.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         <v>1011.602</v>
       </c>
       <c r="H9" t="n">
-        <v>21.49638</v>
+        <v>21.42767</v>
       </c>
       <c r="I9" t="n">
-        <v>13.33321</v>
+        <v>13.25573</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>160.5</v>
+        <v>160.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>1123.254</v>
       </c>
       <c r="H10" t="n">
-        <v>20.396139</v>
+        <v>20.29603</v>
       </c>
       <c r="I10" t="n">
-        <v>11.1759394</v>
+        <v>11.15714</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>128.26</v>
+        <v>128.12</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>215.4</v>
+        <v>215.55</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1187,10 +1187,10 @@
         <v>162.098</v>
       </c>
       <c r="H13" t="n">
-        <v>17.25321</v>
+        <v>17.28042</v>
       </c>
       <c r="I13" t="n">
-        <v>10.02081</v>
+        <v>10.02625</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>323.3</v>
+        <v>324.15</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>294.7</v>
+        <v>292.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>2339.725</v>
       </c>
       <c r="H15" t="n">
-        <v>23.08479</v>
+        <v>22.83368</v>
       </c>
       <c r="I15" t="n">
-        <v>15.550649</v>
+        <v>15.364021</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.905</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         <v>1600.4</v>
       </c>
       <c r="H17" t="n">
-        <v>13.39729</v>
+        <v>13.41088</v>
       </c>
       <c r="I17" t="n">
-        <v>9.542619400000001</v>
+        <v>9.463689499999999</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.86</v>
+        <v>20.76</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>1777.608</v>
       </c>
       <c r="H18" t="n">
-        <v>15.82438</v>
+        <v>15.63901</v>
       </c>
       <c r="I18" t="n">
-        <v>10.74071</v>
+        <v>10.5726</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5729</v>
+        <v>5710</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46.799</v>
+        <v>46.598</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>92.08199999999999</v>
+        <v>91.998</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>24.29</v>
+        <v>24.59</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3.614</v>
+        <v>3.696</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
